--- a/tibetan_associations/tibetan_andean_overlap_significant.xlsx
+++ b/tibetan_associations/tibetan_andean_overlap_significant.xlsx
@@ -1,21 +1,269 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/CMSNetwork/tibetan_associations/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4C69FC-30EE-AD41-BA77-1A0D8ABA3C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="25680" yWindow="660" windowWidth="25380" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+  <si>
+    <t>chr_andean</t>
+  </si>
+  <si>
+    <t>pos_hg37_andean</t>
+  </si>
+  <si>
+    <t>pos_hg38_andean</t>
+  </si>
+  <si>
+    <t>ref_andean</t>
+  </si>
+  <si>
+    <t>alt_andean</t>
+  </si>
+  <si>
+    <t>gene_name</t>
+  </si>
+  <si>
+    <t>gene_symbol</t>
+  </si>
+  <si>
+    <t>v2g_score_andean</t>
+  </si>
+  <si>
+    <t>cms_andean</t>
+  </si>
+  <si>
+    <t>cms_score_andean</t>
+  </si>
+  <si>
+    <t>p_andean</t>
+  </si>
+  <si>
+    <t>xpehh_andean</t>
+  </si>
+  <si>
+    <t>ihs_andean</t>
+  </si>
+  <si>
+    <t>dihh_andean</t>
+  </si>
+  <si>
+    <t>fst_andean</t>
+  </si>
+  <si>
+    <t>daf_andean</t>
+  </si>
+  <si>
+    <t>chr_tibetan</t>
+  </si>
+  <si>
+    <t>pos_hg37_tibetan</t>
+  </si>
+  <si>
+    <t>pos_hg38_tibetan</t>
+  </si>
+  <si>
+    <t>ref_tibetan</t>
+  </si>
+  <si>
+    <t>alt_tibetan</t>
+  </si>
+  <si>
+    <t>v2g_score_tibetan</t>
+  </si>
+  <si>
+    <t>cms_tibetan</t>
+  </si>
+  <si>
+    <t>cms_score_tibetan</t>
+  </si>
+  <si>
+    <t>p_tibetan</t>
+  </si>
+  <si>
+    <t>xpehh_tibetan</t>
+  </si>
+  <si>
+    <t>ihs_tibetan</t>
+  </si>
+  <si>
+    <t>dihh_tibetan</t>
+  </si>
+  <si>
+    <t>fst_tibetan</t>
+  </si>
+  <si>
+    <t>daf_tibetan</t>
+  </si>
+  <si>
+    <t>transformed_beta_tibetan</t>
+  </si>
+  <si>
+    <t>transformed_beta_andean</t>
+  </si>
+  <si>
+    <t>point_color</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>ENSG00000164733</t>
+  </si>
+  <si>
+    <t>CTSB</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>#EF767A</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>ENSG00000100395</t>
+  </si>
+  <si>
+    <t>L3MBTL2</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>ENSG00000100401</t>
+  </si>
+  <si>
+    <t>RANGAP1</t>
+  </si>
+  <si>
+    <t>ENSG00000100412</t>
+  </si>
+  <si>
+    <t>ACO2</t>
+  </si>
+  <si>
+    <t>ENSG00000167074</t>
+  </si>
+  <si>
+    <t>TEF</t>
+  </si>
+  <si>
+    <t>ENSG00000172346</t>
+  </si>
+  <si>
+    <t>CSDC2</t>
+  </si>
+  <si>
+    <t>ENSG00000196236</t>
+  </si>
+  <si>
+    <t>XPNPEP3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>ENSG00000143924</t>
+  </si>
+  <si>
+    <t>EML4</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>ENSG00000019144</t>
+  </si>
+  <si>
+    <t>PHLDB1</t>
+  </si>
+  <si>
+    <t>ENSG00000100393</t>
+  </si>
+  <si>
+    <t>EP300</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ENSG00000114013</t>
+  </si>
+  <si>
+    <t>CD86</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>ENSG00000141002</t>
+  </si>
+  <si>
+    <t>TCF25</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>ENSG00000112303</t>
+  </si>
+  <si>
+    <t>VNN2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>ENSG00000108963</t>
+  </si>
+  <si>
+    <t>DPH1</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>ENSG00000182871</t>
+  </si>
+  <si>
+    <t>COL18A1</t>
+  </si>
+  <si>
+    <t>ENSG00000145979</t>
+  </si>
+  <si>
+    <t>TBC1D7</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +311,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +363,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +397,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +432,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,182 +608,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>chr_andean</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>pos_hg37_andean</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pos_hg38_andean</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ref_andean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>alt_andean</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>gene_name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>gene_symbol</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>v2g_score_andean</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>cms_andean</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>cms_score_andean</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>p_andean</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>xpehh_andean</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ihs_andean</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dihh_andean</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>fst_andean</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>daf_andean</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>chr_tibetan</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pos_hg37_tibetan</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>pos_hg38_tibetan</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ref_tibetan</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>alt_tibetan</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>v2g_score_tibetan</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>cms_tibetan</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>cms_score_tibetan</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>p_tibetan</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>xpehh_tibetan</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ihs_tibetan</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dihh_tibetan</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>fst_tibetan</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>daf_tibetan</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>transformed_beta_tibetan</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>transformed_beta_andean</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>point_color</t>
-        </is>
+    <row r="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>33</v>
       </c>
       <c r="B2">
         <v>11663173</v>
@@ -533,40 +727,32 @@
       <c r="C2">
         <v>11805664</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ENSG00000164733</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CTSB</t>
-        </is>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>37</v>
       </c>
       <c r="H2">
-        <v>0.3386317907444668</v>
+        <v>0.33863179074446681</v>
       </c>
       <c r="I2">
-        <v>-68.7547564678751</v>
+        <v>-68.754756467875097</v>
       </c>
       <c r="J2">
-        <v>16.4504870642498</v>
+        <v>16.450487064249799</v>
       </c>
       <c r="K2">
-        <v>0.00187219262423618</v>
+        <v>1.8721926242361801E-3</v>
       </c>
       <c r="L2">
-        <v>-0.178951079588812</v>
+        <v>-0.17895107958881201</v>
       </c>
       <c r="M2">
         <v>3.32451271854625</v>
@@ -575,15 +761,13 @@
         <v>24087.8945312</v>
       </c>
       <c r="O2">
-        <v>0.320774501686</v>
+        <v>0.32077450168600002</v>
       </c>
       <c r="P2">
-        <v>0.630339805825</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+        <v>0.63033980582500004</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
       <c r="R2">
         <v>11814687</v>
@@ -591,60 +775,52 @@
       <c r="S2">
         <v>11957178</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
       </c>
       <c r="V2">
-        <v>0.2466800804828974</v>
+        <v>0.24668008048289741</v>
       </c>
       <c r="W2">
-        <v>-70.58056049090131</v>
+        <v>-70.580560490901306</v>
       </c>
       <c r="X2">
         <v>11.7696749735761</v>
       </c>
       <c r="Y2">
-        <v>0.000268650393806289</v>
+        <v>2.6865039380628901E-4</v>
       </c>
       <c r="Z2">
         <v>0.125417697656619</v>
       </c>
       <c r="AA2">
-        <v>2.23805517017826</v>
+        <v>2.2380551701782601</v>
       </c>
       <c r="AB2">
-        <v>0.345095574856</v>
+        <v>0.34509557485600001</v>
       </c>
       <c r="AC2">
-        <v>0.09498819065</v>
+        <v>9.4988190649999998E-2</v>
       </c>
       <c r="AD2">
-        <v>0.335125448029</v>
+        <v>0.33512544802900002</v>
       </c>
       <c r="AE2">
-        <v>2.604925957985045</v>
+        <v>2.6049259579850448</v>
       </c>
       <c r="AF2">
         <v>2.794854274355385</v>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+      <c r="AG2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>40</v>
       </c>
       <c r="B3">
         <v>41637119</v>
@@ -652,57 +828,47 @@
       <c r="C3">
         <v>41241115</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ENSG00000100395</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>L3MBTL2</t>
-        </is>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
       </c>
       <c r="H3">
-        <v>0.2533199195171026</v>
+        <v>0.25331991951710259</v>
       </c>
       <c r="I3">
-        <v>-69.55745068314791</v>
+        <v>-69.557450683147906</v>
       </c>
       <c r="J3">
         <v>14.8450986337042</v>
       </c>
       <c r="K3">
-        <v>0.0028725259007219</v>
+        <v>2.8725259007219002E-3</v>
       </c>
       <c r="L3">
-        <v>1.35414686912355</v>
+        <v>1.3541468691235501</v>
       </c>
       <c r="M3">
-        <v>2.37768739815043</v>
+        <v>2.3776873981504298</v>
       </c>
       <c r="N3">
         <v>451977.15625</v>
       </c>
       <c r="O3">
-        <v>0.39726623902</v>
+        <v>0.39726623902000002</v>
       </c>
       <c r="P3">
-        <v>0.620266990291</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.62026699029099996</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
       </c>
       <c r="R3">
         <v>41597377</v>
@@ -710,60 +876,52 @@
       <c r="S3">
         <v>41201373</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="T3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
+        <v>43</v>
       </c>
       <c r="V3">
-        <v>0.2663983903420523</v>
+        <v>0.26639839034205232</v>
       </c>
       <c r="W3">
-        <v>-65.86963311966051</v>
+        <v>-65.869633119660506</v>
       </c>
       <c r="X3">
-        <v>21.189047057333</v>
+        <v>21.189047057332999</v>
       </c>
       <c r="Y3">
-        <v>3.11282572168496E-05</v>
+        <v>3.1128257216849603E-5</v>
       </c>
       <c r="Z3">
-        <v>4.25922500906369</v>
+        <v>4.2592250090636901</v>
       </c>
       <c r="AA3">
-        <v>0.9731608429745</v>
+        <v>0.97316084297450001</v>
       </c>
       <c r="AB3">
-        <v>0.00747241731733</v>
+        <v>7.4724173173300002E-3</v>
       </c>
       <c r="AC3">
         <v>0.156265556551</v>
       </c>
       <c r="AD3">
-        <v>0.428614097969</v>
+        <v>0.42861409796900002</v>
       </c>
       <c r="AE3">
-        <v>3.093372384807794</v>
+        <v>3.0933723848077941</v>
       </c>
       <c r="AF3">
-        <v>2.516456743915258</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.5164567439152581</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>40</v>
       </c>
       <c r="B4">
         <v>41637119</v>
@@ -771,57 +929,47 @@
       <c r="C4">
         <v>41241115</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ENSG00000100401</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>RANGAP1</t>
-        </is>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
       </c>
       <c r="H4">
-        <v>0.3140845070422535</v>
+        <v>0.31408450704225349</v>
       </c>
       <c r="I4">
-        <v>-69.55745068314791</v>
+        <v>-69.557450683147906</v>
       </c>
       <c r="J4">
         <v>14.8450986337042</v>
       </c>
       <c r="K4">
-        <v>0.0028725259007219</v>
+        <v>2.8725259007219002E-3</v>
       </c>
       <c r="L4">
-        <v>1.35414686912355</v>
+        <v>1.3541468691235501</v>
       </c>
       <c r="M4">
-        <v>2.37768739815043</v>
+        <v>2.3776873981504298</v>
       </c>
       <c r="N4">
         <v>451977.15625</v>
       </c>
       <c r="O4">
-        <v>0.39726623902</v>
+        <v>0.39726623902000002</v>
       </c>
       <c r="P4">
-        <v>0.620266990291</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.62026699029099996</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
       </c>
       <c r="R4">
         <v>41627775</v>
@@ -829,60 +977,52 @@
       <c r="S4">
         <v>41231771</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="T4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" t="s">
+        <v>38</v>
       </c>
       <c r="V4">
-        <v>0.2939637826961771</v>
+        <v>0.29396378269617712</v>
       </c>
       <c r="W4">
-        <v>-67.4167723522814</v>
+        <v>-67.416772352281399</v>
       </c>
       <c r="X4">
-        <v>18.0955839344668</v>
+        <v>18.095583934466799</v>
       </c>
       <c r="Y4">
-        <v>6.5640020652922E-05</v>
+        <v>6.5640020652922001E-5</v>
       </c>
       <c r="Z4">
-        <v>4.67062085033923</v>
+        <v>4.6706208503392297</v>
       </c>
       <c r="AA4">
-        <v>0.795914182510205</v>
+        <v>0.79591418251020496</v>
       </c>
       <c r="AB4">
-        <v>0.00200907234102</v>
+        <v>2.0090723410200002E-3</v>
       </c>
       <c r="AC4">
-        <v>0.14482835867</v>
+        <v>0.14482835866999999</v>
       </c>
       <c r="AD4">
-        <v>0.387992831541</v>
+        <v>0.38799283154100001</v>
       </c>
       <c r="AE4">
         <v>2.883060393637868</v>
       </c>
       <c r="AF4">
-        <v>2.516456743915258</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.5164567439152581</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>40</v>
       </c>
       <c r="B5">
         <v>41637119</v>
@@ -890,57 +1030,47 @@
       <c r="C5">
         <v>41241115</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ENSG00000100412</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ACO2</t>
-        </is>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
       </c>
       <c r="H5">
         <v>0.2209255533199195</v>
       </c>
       <c r="I5">
-        <v>-69.55745068314791</v>
+        <v>-69.557450683147906</v>
       </c>
       <c r="J5">
         <v>14.8450986337042</v>
       </c>
       <c r="K5">
-        <v>0.0028725259007219</v>
+        <v>2.8725259007219002E-3</v>
       </c>
       <c r="L5">
-        <v>1.35414686912355</v>
+        <v>1.3541468691235501</v>
       </c>
       <c r="M5">
-        <v>2.37768739815043</v>
+        <v>2.3776873981504298</v>
       </c>
       <c r="N5">
         <v>451977.15625</v>
       </c>
       <c r="O5">
-        <v>0.39726623902</v>
+        <v>0.39726623902000002</v>
       </c>
       <c r="P5">
-        <v>0.620266990291</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.62026699029099996</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>40</v>
       </c>
       <c r="R5">
         <v>41627775</v>
@@ -948,60 +1078,52 @@
       <c r="S5">
         <v>41231771</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="T5" t="s">
+        <v>43</v>
+      </c>
+      <c r="U5" t="s">
+        <v>38</v>
       </c>
       <c r="V5">
         <v>0.2209255533199195</v>
       </c>
       <c r="W5">
-        <v>-67.4167723522814</v>
+        <v>-67.416772352281399</v>
       </c>
       <c r="X5">
-        <v>18.0955839344668</v>
+        <v>18.095583934466799</v>
       </c>
       <c r="Y5">
-        <v>6.5640020652922E-05</v>
+        <v>6.5640020652922001E-5</v>
       </c>
       <c r="Z5">
-        <v>4.67062085033923</v>
+        <v>4.6706208503392297</v>
       </c>
       <c r="AA5">
-        <v>0.795914182510205</v>
+        <v>0.79591418251020496</v>
       </c>
       <c r="AB5">
-        <v>0.00200907234102</v>
+        <v>2.0090723410200002E-3</v>
       </c>
       <c r="AC5">
-        <v>0.14482835867</v>
+        <v>0.14482835866999999</v>
       </c>
       <c r="AD5">
-        <v>0.387992831541</v>
+        <v>0.38799283154100001</v>
       </c>
       <c r="AE5">
         <v>2.883060393637868</v>
       </c>
       <c r="AF5">
-        <v>2.516456743915258</v>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.5164567439152581</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>40</v>
       </c>
       <c r="B6">
         <v>41637119</v>
@@ -1009,57 +1131,47 @@
       <c r="C6">
         <v>41241115</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ENSG00000167074</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TEF</t>
-        </is>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>0.2191146881287726</v>
+        <v>0.21911468812877261</v>
       </c>
       <c r="I6">
-        <v>-69.55745068314791</v>
+        <v>-69.557450683147906</v>
       </c>
       <c r="J6">
         <v>14.8450986337042</v>
       </c>
       <c r="K6">
-        <v>0.0028725259007219</v>
+        <v>2.8725259007219002E-3</v>
       </c>
       <c r="L6">
-        <v>1.35414686912355</v>
+        <v>1.3541468691235501</v>
       </c>
       <c r="M6">
-        <v>2.37768739815043</v>
+        <v>2.3776873981504298</v>
       </c>
       <c r="N6">
         <v>451977.15625</v>
       </c>
       <c r="O6">
-        <v>0.39726623902</v>
+        <v>0.39726623902000002</v>
       </c>
       <c r="P6">
-        <v>0.620266990291</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.62026699029099996</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
       </c>
       <c r="R6">
         <v>41627775</v>
@@ -1067,60 +1179,52 @@
       <c r="S6">
         <v>41231771</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="T6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" t="s">
+        <v>38</v>
       </c>
       <c r="V6">
-        <v>0.2191146881287726</v>
+        <v>0.21911468812877261</v>
       </c>
       <c r="W6">
-        <v>-67.4167723522814</v>
+        <v>-67.416772352281399</v>
       </c>
       <c r="X6">
-        <v>18.0955839344668</v>
+        <v>18.095583934466799</v>
       </c>
       <c r="Y6">
-        <v>6.5640020652922E-05</v>
+        <v>6.5640020652922001E-5</v>
       </c>
       <c r="Z6">
-        <v>4.67062085033923</v>
+        <v>4.6706208503392297</v>
       </c>
       <c r="AA6">
-        <v>0.795914182510205</v>
+        <v>0.79591418251020496</v>
       </c>
       <c r="AB6">
-        <v>0.00200907234102</v>
+        <v>2.0090723410200002E-3</v>
       </c>
       <c r="AC6">
-        <v>0.14482835867</v>
+        <v>0.14482835866999999</v>
       </c>
       <c r="AD6">
-        <v>0.387992831541</v>
+        <v>0.38799283154100001</v>
       </c>
       <c r="AE6">
         <v>2.883060393637868</v>
       </c>
       <c r="AF6">
-        <v>2.516456743915258</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.5164567439152581</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>40</v>
       </c>
       <c r="B7">
         <v>41637119</v>
@@ -1128,57 +1232,47 @@
       <c r="C7">
         <v>41241115</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ENSG00000172346</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CSDC2</t>
-        </is>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
       </c>
       <c r="H7">
-        <v>0.3201207243460764</v>
+        <v>0.32012072434607641</v>
       </c>
       <c r="I7">
-        <v>-69.55745068314791</v>
+        <v>-69.557450683147906</v>
       </c>
       <c r="J7">
         <v>14.8450986337042</v>
       </c>
       <c r="K7">
-        <v>0.0028725259007219</v>
+        <v>2.8725259007219002E-3</v>
       </c>
       <c r="L7">
-        <v>1.35414686912355</v>
+        <v>1.3541468691235501</v>
       </c>
       <c r="M7">
-        <v>2.37768739815043</v>
+        <v>2.3776873981504298</v>
       </c>
       <c r="N7">
         <v>451977.15625</v>
       </c>
       <c r="O7">
-        <v>0.39726623902</v>
+        <v>0.39726623902000002</v>
       </c>
       <c r="P7">
-        <v>0.620266990291</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.62026699029099996</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>40</v>
       </c>
       <c r="R7">
         <v>41627775</v>
@@ -1186,60 +1280,52 @@
       <c r="S7">
         <v>41231771</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="T7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U7" t="s">
+        <v>38</v>
       </c>
       <c r="V7">
-        <v>0.3002012072434607</v>
+        <v>0.30020120724346072</v>
       </c>
       <c r="W7">
-        <v>-67.4167723522814</v>
+        <v>-67.416772352281399</v>
       </c>
       <c r="X7">
-        <v>18.0955839344668</v>
+        <v>18.095583934466799</v>
       </c>
       <c r="Y7">
-        <v>6.5640020652922E-05</v>
+        <v>6.5640020652922001E-5</v>
       </c>
       <c r="Z7">
-        <v>4.67062085033923</v>
+        <v>4.6706208503392297</v>
       </c>
       <c r="AA7">
-        <v>0.795914182510205</v>
+        <v>0.79591418251020496</v>
       </c>
       <c r="AB7">
-        <v>0.00200907234102</v>
+        <v>2.0090723410200002E-3</v>
       </c>
       <c r="AC7">
-        <v>0.14482835867</v>
+        <v>0.14482835866999999</v>
       </c>
       <c r="AD7">
-        <v>0.387992831541</v>
+        <v>0.38799283154100001</v>
       </c>
       <c r="AE7">
         <v>2.883060393637868</v>
       </c>
       <c r="AF7">
-        <v>2.516456743915258</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.5164567439152581</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>40</v>
       </c>
       <c r="B8">
         <v>41637119</v>
@@ -1247,57 +1333,47 @@
       <c r="C8">
         <v>41241115</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ENSG00000196236</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>XPNPEP3</t>
-        </is>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
       </c>
       <c r="H8">
-        <v>0.2603621730382293</v>
+        <v>0.26036217303822928</v>
       </c>
       <c r="I8">
-        <v>-69.55745068314791</v>
+        <v>-69.557450683147906</v>
       </c>
       <c r="J8">
         <v>14.8450986337042</v>
       </c>
       <c r="K8">
-        <v>0.0028725259007219</v>
+        <v>2.8725259007219002E-3</v>
       </c>
       <c r="L8">
-        <v>1.35414686912355</v>
+        <v>1.3541468691235501</v>
       </c>
       <c r="M8">
-        <v>2.37768739815043</v>
+        <v>2.3776873981504298</v>
       </c>
       <c r="N8">
         <v>451977.15625</v>
       </c>
       <c r="O8">
-        <v>0.39726623902</v>
+        <v>0.39726623902000002</v>
       </c>
       <c r="P8">
-        <v>0.620266990291</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.62026699029099996</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>40</v>
       </c>
       <c r="R8">
         <v>41626663</v>
@@ -1305,60 +1381,52 @@
       <c r="S8">
         <v>41230659</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
+      <c r="T8" t="s">
+        <v>43</v>
+      </c>
+      <c r="U8" t="s">
+        <v>34</v>
       </c>
       <c r="V8">
-        <v>0.2336016096579477</v>
+        <v>0.23360160965794771</v>
       </c>
       <c r="W8">
-        <v>-65.86963311966051</v>
+        <v>-65.869633119660506</v>
       </c>
       <c r="X8">
-        <v>21.189047057333</v>
+        <v>21.189047057332999</v>
       </c>
       <c r="Y8">
-        <v>3.11282572168496E-05</v>
+        <v>3.1128257216849603E-5</v>
       </c>
       <c r="Z8">
-        <v>4.62245484457246</v>
+        <v>4.6224548445724603</v>
       </c>
       <c r="AA8">
-        <v>0.906172984995013</v>
+        <v>0.90617298499501298</v>
       </c>
       <c r="AB8">
-        <v>0.008583991788329999</v>
+        <v>8.5839917883299994E-3</v>
       </c>
       <c r="AC8">
         <v>0.162510916078</v>
       </c>
       <c r="AD8">
-        <v>0.436678614098</v>
+        <v>0.43667861409800002</v>
       </c>
       <c r="AE8">
-        <v>3.093372384807794</v>
+        <v>3.0933723848077941</v>
       </c>
       <c r="AF8">
-        <v>2.516456743915258</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.5164567439152581</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>54</v>
       </c>
       <c r="B9">
         <v>42607288</v>
@@ -1366,43 +1434,35 @@
       <c r="C9">
         <v>42380148</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ENSG00000143924</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>EML4</t>
-        </is>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
       </c>
       <c r="H9">
-        <v>0.3070422535211267</v>
+        <v>0.30704225352112668</v>
       </c>
       <c r="I9">
-        <v>-69.7647390261692</v>
+        <v>-69.764739026169195</v>
       </c>
       <c r="J9">
         <v>14.4305219476616</v>
       </c>
       <c r="K9">
-        <v>0.00321990932763547</v>
+        <v>3.2199093276354699E-3</v>
       </c>
       <c r="L9">
         <v>2.47199474222356</v>
       </c>
       <c r="M9">
-        <v>1.95985303489154</v>
+        <v>1.9598530348915399</v>
       </c>
       <c r="N9">
         <v>149731.453125</v>
@@ -1411,12 +1471,10 @@
         <v>0.35536407767</v>
       </c>
       <c r="P9">
-        <v>0.646116504854</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+        <v>0.64611650485399996</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>54</v>
       </c>
       <c r="R9">
         <v>42324396</v>
@@ -1424,42 +1482,38 @@
       <c r="S9">
         <v>42097256</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="T9" t="s">
+        <v>38</v>
+      </c>
+      <c r="U9" t="s">
+        <v>43</v>
       </c>
       <c r="V9">
-        <v>0.258953722334004</v>
+        <v>0.25895372233400399</v>
       </c>
       <c r="W9">
-        <v>-68.0753361530634</v>
+        <v>-68.075336153063404</v>
       </c>
       <c r="X9">
-        <v>16.7788033960258</v>
+        <v>16.778803396025801</v>
       </c>
       <c r="Y9">
-        <v>9.067796667517051E-05</v>
+        <v>9.0677966675170506E-5</v>
       </c>
       <c r="Z9">
-        <v>1.91073569417688</v>
+        <v>1.9107356941768801</v>
       </c>
       <c r="AA9">
         <v>2.3469253347949</v>
       </c>
       <c r="AB9">
-        <v>0.132034227252</v>
+        <v>0.13203422725200001</v>
       </c>
       <c r="AC9">
-        <v>0.102705988388</v>
+        <v>0.10270598838800001</v>
       </c>
       <c r="AD9">
-        <v>0.334528076464</v>
+        <v>0.33452807646400001</v>
       </c>
       <c r="AE9">
         <v>2.790007259634808</v>
@@ -1467,17 +1521,13 @@
       <c r="AF9">
         <v>2.478692003928781</v>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+      <c r="AG9" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>57</v>
       </c>
       <c r="B10">
         <v>118608625</v>
@@ -1485,40 +1535,32 @@
       <c r="C10">
         <v>118737916</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ENSG00000019144</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PHLDB1</t>
-        </is>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
       </c>
       <c r="H10">
         <v>0.2340040241448692</v>
       </c>
       <c r="I10">
-        <v>-70.50197781756211</v>
+        <v>-70.501977817562107</v>
       </c>
       <c r="J10">
-        <v>12.9560443648758</v>
+        <v>12.956044364875799</v>
       </c>
       <c r="K10">
-        <v>0.00481399368260944</v>
+        <v>4.8139936826094402E-3</v>
       </c>
       <c r="L10">
-        <v>2.22566092791642</v>
+        <v>2.2256609279164201</v>
       </c>
       <c r="M10">
         <v>3.48539487554073</v>
@@ -1527,15 +1569,13 @@
         <v>181995.96875</v>
       </c>
       <c r="O10">
-        <v>0.156901342657</v>
+        <v>0.15690134265700001</v>
       </c>
       <c r="P10">
-        <v>0.438106796117</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>0.43810679611699999</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>57</v>
       </c>
       <c r="R10">
         <v>118705753</v>
@@ -1543,60 +1583,52 @@
       <c r="S10">
         <v>118835044</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="T10" t="s">
+        <v>38</v>
+      </c>
+      <c r="U10" t="s">
+        <v>35</v>
       </c>
       <c r="V10">
-        <v>0.2074446680080483</v>
+        <v>0.20744466800804831</v>
       </c>
       <c r="W10">
-        <v>-69.7608278536931</v>
+        <v>-69.760827853693101</v>
       </c>
       <c r="X10">
-        <v>13.4087082488927</v>
+        <v>13.408708248892699</v>
       </c>
       <c r="Y10">
-        <v>0.000177295725887274</v>
+        <v>1.7729572588727401E-4</v>
       </c>
       <c r="Z10">
-        <v>4.36538546637505</v>
+        <v>4.3653854663750504</v>
       </c>
       <c r="AA10">
         <v>1.58241961610738</v>
       </c>
       <c r="AB10">
-        <v>0.0378147475421</v>
+        <v>3.78147475421E-2</v>
       </c>
       <c r="AC10">
         <v>0.107329714664</v>
       </c>
       <c r="AD10">
-        <v>0.349761051374</v>
+        <v>0.34976105137399999</v>
       </c>
       <c r="AE10">
-        <v>2.641707854509278</v>
+        <v>2.6417078545092778</v>
       </c>
       <c r="AF10">
-        <v>2.323322325168575</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.3233223251685748</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>40</v>
       </c>
       <c r="B11">
         <v>41613188</v>
@@ -1604,57 +1636,47 @@
       <c r="C11">
         <v>41217184</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ENSG00000100393</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EP300</t>
-        </is>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
       </c>
       <c r="H11">
         <v>0.2058350100603622</v>
       </c>
       <c r="I11">
-        <v>-71.5055551842903</v>
+        <v>-71.505555184290301</v>
       </c>
       <c r="J11">
         <v>10.9488896314194</v>
       </c>
       <c r="K11">
-        <v>0.00813189586961357</v>
+        <v>8.1318958696135705E-3</v>
       </c>
       <c r="L11">
-        <v>1.28973417322467</v>
+        <v>1.2897341732246701</v>
       </c>
       <c r="M11">
-        <v>1.91004630511668</v>
+        <v>1.9100463051166801</v>
       </c>
       <c r="N11">
         <v>403373.8125</v>
       </c>
       <c r="O11">
-        <v>0.338833031438</v>
+        <v>0.33883303143799998</v>
       </c>
       <c r="P11">
-        <v>0.5654126213589999</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>0.56541262135899995</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>40</v>
       </c>
       <c r="R11">
         <v>41598874</v>
@@ -1662,60 +1684,52 @@
       <c r="S11">
         <v>41202870</v>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="T11" t="s">
+        <v>38</v>
+      </c>
+      <c r="U11" t="s">
+        <v>35</v>
       </c>
       <c r="V11">
         <v>0.2128772635814889</v>
       </c>
       <c r="W11">
-        <v>-65.86963311966051</v>
+        <v>-65.869633119660506</v>
       </c>
       <c r="X11">
-        <v>21.189047057333</v>
+        <v>21.189047057332999</v>
       </c>
       <c r="Y11">
-        <v>3.11282572168496E-05</v>
+        <v>3.1128257216849603E-5</v>
       </c>
       <c r="Z11">
-        <v>4.27205400958428</v>
+        <v>4.2720540095842798</v>
       </c>
       <c r="AA11">
-        <v>0.977231022136998</v>
+        <v>0.97723102213699797</v>
       </c>
       <c r="AB11">
-        <v>0.00751496851444</v>
+        <v>7.5149685144399996E-3</v>
       </c>
       <c r="AC11">
         <v>0.156265556551</v>
       </c>
       <c r="AD11">
-        <v>0.428614097969</v>
+        <v>0.42861409796900002</v>
       </c>
       <c r="AE11">
-        <v>3.093372384807794</v>
+        <v>3.0933723848077941</v>
       </c>
       <c r="AF11">
-        <v>2.076210536379371</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>2.0762105363793708</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>62</v>
       </c>
       <c r="B12">
         <v>121821143</v>
@@ -1723,57 +1737,47 @@
       <c r="C12">
         <v>122102296</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ENSG00000114013</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CD86</t>
-        </is>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
       </c>
       <c r="H12">
-        <v>0.2458752515090543</v>
+        <v>0.24587525150905429</v>
       </c>
       <c r="I12">
-        <v>-72.14857935796771</v>
+        <v>-72.148579357967705</v>
       </c>
       <c r="J12">
-        <v>9.6628412840646</v>
+        <v>9.6628412840645996</v>
       </c>
       <c r="K12">
-        <v>0.0113306447854574</v>
+        <v>1.13306447854574E-2</v>
       </c>
       <c r="L12">
-        <v>1.48664982754674</v>
+        <v>1.4866498275467399</v>
       </c>
       <c r="M12">
-        <v>1.01767337984345</v>
+        <v>1.0176733798434501</v>
       </c>
       <c r="N12">
         <v>106565.304688</v>
       </c>
       <c r="O12">
-        <v>0.324958673037</v>
+        <v>0.32495867303699999</v>
       </c>
       <c r="P12">
-        <v>0.633737864078</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+        <v>0.63373786407800003</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>62</v>
       </c>
       <c r="R12">
         <v>121805228</v>
@@ -1781,42 +1785,38 @@
       <c r="S12">
         <v>122086381</v>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
+      <c r="T12" t="s">
+        <v>43</v>
+      </c>
+      <c r="U12" t="s">
+        <v>34</v>
       </c>
       <c r="V12">
-        <v>0.2193158953722334</v>
+        <v>0.21931589537223339</v>
       </c>
       <c r="W12">
-        <v>-71.26237450024151</v>
+        <v>-71.262374500241506</v>
       </c>
       <c r="X12">
         <v>10.4064062708786</v>
       </c>
       <c r="Y12">
-        <v>0.000357298256749926</v>
+        <v>3.5729825674992599E-4</v>
       </c>
       <c r="Z12">
-        <v>-2.80464679717202</v>
+        <v>-2.8046467971720199</v>
       </c>
       <c r="AA12">
         <v>1.41394982776439</v>
       </c>
       <c r="AB12">
-        <v>0.0900330841541</v>
+        <v>9.0033084154099996E-2</v>
       </c>
       <c r="AC12">
-        <v>0.122436985765</v>
+        <v>0.12243698576500001</v>
       </c>
       <c r="AD12">
-        <v>0.268817204301</v>
+        <v>0.26881720430099998</v>
       </c>
       <c r="AE12">
         <v>2.560791409765526</v>
@@ -1824,17 +1824,13 @@
       <c r="AF12">
         <v>1.883278779113011</v>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+      <c r="AG12" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>65</v>
       </c>
       <c r="B13">
         <v>89522747</v>
@@ -1842,37 +1838,29 @@
       <c r="C13">
         <v>89456339</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ENSG00000141002</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>TCF25</t>
-        </is>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
       </c>
       <c r="H13">
-        <v>0.2603621730382293</v>
+        <v>0.26036217303822928</v>
       </c>
       <c r="I13">
-        <v>-72.4343039161983</v>
+        <v>-72.434303916198303</v>
       </c>
       <c r="J13">
-        <v>9.0913921676034</v>
+        <v>9.0913921676034004</v>
       </c>
       <c r="K13">
-        <v>0.0130159204388669</v>
+        <v>1.30159204388669E-2</v>
       </c>
       <c r="L13">
         <v>0.129288316376934</v>
@@ -1884,15 +1872,13 @@
         <v>201722.609375</v>
       </c>
       <c r="O13">
-        <v>0.342751483279</v>
+        <v>0.34275148327900001</v>
       </c>
       <c r="P13">
-        <v>0.432645631068</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+        <v>0.43264563106800003</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>65</v>
       </c>
       <c r="R13">
         <v>89833881</v>
@@ -1900,42 +1886,38 @@
       <c r="S13">
         <v>89767473</v>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
+      <c r="T13" t="s">
+        <v>38</v>
+      </c>
+      <c r="U13" t="s">
+        <v>34</v>
       </c>
       <c r="V13">
         <v>0.2004024144869215</v>
       </c>
       <c r="W13">
-        <v>-73.0131645235937</v>
+        <v>-73.013164523593701</v>
       </c>
       <c r="X13">
-        <v>6.90574889051652</v>
+        <v>6.9057488905165201</v>
       </c>
       <c r="Y13">
-        <v>0.000725423733401364</v>
+        <v>7.2542373340136405E-4</v>
       </c>
       <c r="Z13">
-        <v>-1.49767261668918</v>
+        <v>-1.4976726166891801</v>
       </c>
       <c r="AA13">
         <v>-2.43334598257707</v>
       </c>
       <c r="AB13">
-        <v>0.0164839122444</v>
+        <v>1.64839122444E-2</v>
       </c>
       <c r="AC13">
         <v>0.260984180126</v>
       </c>
       <c r="AD13">
-        <v>0.372759856631</v>
+        <v>0.37275985663099998</v>
       </c>
       <c r="AE13">
         <v>2.374442268150776</v>
@@ -1943,17 +1925,13 @@
       <c r="AF13">
         <v>1.829376003108846</v>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+      <c r="AG13" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>68</v>
       </c>
       <c r="B14">
         <v>133073425</v>
@@ -1961,57 +1939,47 @@
       <c r="C14">
         <v>132752286</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ENSG00000112303</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VNN2</t>
-        </is>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
       </c>
       <c r="H14">
-        <v>0.4004024144869215</v>
+        <v>0.40040241448692149</v>
       </c>
       <c r="I14">
-        <v>-72.9535594281878</v>
+        <v>-72.953559428187802</v>
       </c>
       <c r="J14">
-        <v>8.052881143624401</v>
+        <v>8.0528811436244006</v>
       </c>
       <c r="K14">
-        <v>0.0167454430171523</v>
+        <v>1.6745443017152299E-2</v>
       </c>
       <c r="L14">
-        <v>-1.46734702476438</v>
+        <v>-1.4673470247643801</v>
       </c>
       <c r="M14">
-        <v>2.41260524533533</v>
+        <v>2.4126052453353299</v>
       </c>
       <c r="N14">
         <v>211140.515625</v>
       </c>
       <c r="O14">
-        <v>0.205436893204</v>
+        <v>0.20543689320399999</v>
       </c>
       <c r="P14">
-        <v>0.290291262136</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>0.29029126213599998</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>68</v>
       </c>
       <c r="R14">
         <v>133069713</v>
@@ -2019,36 +1987,32 @@
       <c r="S14">
         <v>132748574</v>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
+      <c r="T14" t="s">
+        <v>43</v>
+      </c>
+      <c r="U14" t="s">
+        <v>34</v>
       </c>
       <c r="V14">
-        <v>0.420523138832998</v>
+        <v>0.42052313883299802</v>
       </c>
       <c r="W14">
-        <v>-69.19801438779621</v>
+        <v>-69.198014387796206</v>
       </c>
       <c r="X14">
         <v>14.5340385779899</v>
       </c>
       <c r="Y14">
-        <v>0.000138047053744289</v>
+        <v>1.38047053744289E-4</v>
       </c>
       <c r="Z14">
         <v>-2.09600254470373</v>
       </c>
       <c r="AA14">
-        <v>-0.630697836482664</v>
+        <v>-0.63069783648266398</v>
       </c>
       <c r="AB14">
-        <v>0.0793155506253</v>
+        <v>7.9315550625300005E-2</v>
       </c>
       <c r="AC14">
         <v>0.168477754073</v>
@@ -2062,17 +2026,13 @@
       <c r="AF14">
         <v>1.697087939295612</v>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+      <c r="AG14" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>71</v>
       </c>
       <c r="B15">
         <v>2128865</v>
@@ -2080,57 +2040,47 @@
       <c r="C15">
         <v>2225571</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ENSG00000108963</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DPH1</t>
-        </is>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
       </c>
       <c r="H15">
-        <v>0.2796780684104628</v>
+        <v>0.27967806841046278</v>
       </c>
       <c r="I15">
-        <v>-73.34687643499809</v>
+        <v>-73.346876434998094</v>
       </c>
       <c r="J15">
-        <v>7.26624713000382</v>
+        <v>7.2662471300038201</v>
       </c>
       <c r="K15">
-        <v>0.020056039823895</v>
+        <v>2.0056039823894999E-2</v>
       </c>
       <c r="L15">
-        <v>-1.16760152629413</v>
+        <v>-1.1676015262941299</v>
       </c>
       <c r="M15">
-        <v>1.48228012639469</v>
+        <v>1.4822801263946901</v>
       </c>
       <c r="N15">
         <v>89961.78125</v>
       </c>
       <c r="O15">
-        <v>0.267378640777</v>
+        <v>0.26737864077700002</v>
       </c>
       <c r="P15">
-        <v>0.482766990291</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>0.48276699029100001</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>71</v>
       </c>
       <c r="R15">
         <v>1931655</v>
@@ -2138,33 +2088,29 @@
       <c r="S15">
         <v>2028361</v>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
+      <c r="T15" t="s">
+        <v>35</v>
+      </c>
+      <c r="U15" t="s">
+        <v>38</v>
       </c>
       <c r="V15">
-        <v>0.3802816901408451</v>
+        <v>0.38028169014084512</v>
       </c>
       <c r="W15">
-        <v>-68.3483639386033</v>
+        <v>-68.348363938603299</v>
       </c>
       <c r="X15">
-        <v>16.232891710589</v>
+        <v>16.232891710589001</v>
       </c>
       <c r="Y15">
-        <v>0.000100828485332839</v>
+        <v>1.00828485332839E-4</v>
       </c>
       <c r="Z15">
-        <v>0.989264620443369</v>
+        <v>0.98926462044336905</v>
       </c>
       <c r="AA15">
-        <v>1.22352290344951</v>
+        <v>1.2235229034495101</v>
       </c>
       <c r="AB15">
         <v>0.112579882145</v>
@@ -2179,19 +2125,15 @@
         <v>2.753416454972363</v>
       </c>
       <c r="AF15">
-        <v>1.590583793676393</v>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>1.5905837936763929</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>74</v>
       </c>
       <c r="B16">
         <v>46921566</v>
@@ -2199,57 +2141,47 @@
       <c r="C16">
         <v>45501652</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ENSG00000182871</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>COL18A1</t>
-        </is>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
       </c>
       <c r="H16">
         <v>0.2128772635814889</v>
       </c>
       <c r="I16">
-        <v>-73.5594255719443</v>
+        <v>-73.559425571944303</v>
       </c>
       <c r="J16">
         <v>6.8411488561114</v>
       </c>
       <c r="K16">
-        <v>0.0220458742613064</v>
+        <v>2.20458742613064E-2</v>
       </c>
       <c r="L16">
-        <v>-1.05907023946064</v>
+        <v>-1.0590702394606399</v>
       </c>
       <c r="M16">
-        <v>2.23772205056918</v>
+        <v>2.2377220505691802</v>
       </c>
       <c r="N16">
         <v>85600.921875</v>
       </c>
       <c r="O16">
-        <v>0.225190114068</v>
+        <v>0.22519011406799999</v>
       </c>
       <c r="P16">
-        <v>0.2875</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>74</v>
       </c>
       <c r="R16">
         <v>46843004</v>
@@ -2257,15 +2189,11 @@
       <c r="S16">
         <v>45423089</v>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
+      <c r="T16" t="s">
+        <v>34</v>
+      </c>
+      <c r="U16" t="s">
+        <v>43</v>
       </c>
       <c r="V16">
         <v>0.2474849094567404</v>
@@ -2274,43 +2202,39 @@
         <v>-72.6319715801543</v>
       </c>
       <c r="X16">
-        <v>7.66793388871412</v>
+        <v>7.6679338887141197</v>
       </c>
       <c r="Y16">
-        <v>0.000630008858019282</v>
+        <v>6.3000885801928197E-4</v>
       </c>
       <c r="Z16">
         <v>3.20157990520419</v>
       </c>
       <c r="AA16">
-        <v>2.06742686513127</v>
+        <v>2.0674268651312699</v>
       </c>
       <c r="AB16">
-        <v>0.0744191482663</v>
+        <v>7.44191482663E-2</v>
       </c>
       <c r="AC16">
-        <v>0.08741436566870001</v>
+        <v>8.7414365668700006E-2</v>
       </c>
       <c r="AD16">
-        <v>0.321385902031</v>
+        <v>0.32138590203099998</v>
       </c>
       <c r="AE16">
         <v>2.425136695648018</v>
       </c>
       <c r="AF16">
-        <v>1.544286436934435</v>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>1.5442864369344349</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>68</v>
       </c>
       <c r="B17">
         <v>13284922</v>
@@ -2318,57 +2242,47 @@
       <c r="C17">
         <v>13284690</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ENSG00000145979</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>TBC1D7</t>
-        </is>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
       </c>
       <c r="H17">
         <v>0.2464788732394366</v>
       </c>
       <c r="I17">
-        <v>-73.5726940275372</v>
+        <v>-73.572694027537196</v>
       </c>
       <c r="J17">
-        <v>6.81461194492562</v>
+        <v>6.8146119449256197</v>
       </c>
       <c r="K17">
-        <v>0.0221836688476166</v>
+        <v>2.2183668847616599E-2</v>
       </c>
       <c r="L17">
-        <v>0.473363466064349</v>
+        <v>0.47336346606434898</v>
       </c>
       <c r="M17">
-        <v>0.726424493642423</v>
+        <v>0.72642449364242301</v>
       </c>
       <c r="N17">
         <v>53444.6445312</v>
       </c>
       <c r="O17">
-        <v>0.410955428067</v>
+        <v>0.41095542806699997</v>
       </c>
       <c r="P17">
-        <v>0.515291262136</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>0.51529126213599996</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>68</v>
       </c>
       <c r="R17">
         <v>13317084</v>
@@ -2376,53 +2290,47 @@
       <c r="S17">
         <v>13316852</v>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+      <c r="T17" t="s">
+        <v>43</v>
+      </c>
+      <c r="U17" t="s">
+        <v>35</v>
       </c>
       <c r="V17">
-        <v>0.3468812877263581</v>
+        <v>0.34688128772635812</v>
       </c>
       <c r="W17">
-        <v>-68.6014342244753</v>
+        <v>-68.601434224475298</v>
       </c>
       <c r="X17">
         <v>15.7268845068857</v>
       </c>
       <c r="Y17">
-        <v>0.000107595497771284</v>
+        <v>1.0759549777128401E-4</v>
       </c>
       <c r="Z17">
-        <v>2.82682501012165</v>
+        <v>2.8268250101216501</v>
       </c>
       <c r="AA17">
         <v>1.33955148828152</v>
       </c>
       <c r="AB17">
-        <v>0.00139081478119</v>
+        <v>1.39081478119E-3</v>
       </c>
       <c r="AC17">
-        <v>0.157360323555</v>
+        <v>0.15736032355499999</v>
       </c>
       <c r="AD17">
-        <v>0.426821983274</v>
+        <v>0.42682198327400001</v>
       </c>
       <c r="AE17">
-        <v>2.720178008967641</v>
+        <v>2.7201780089676411</v>
       </c>
       <c r="AF17">
-        <v>1.538486536020018</v>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>#EF767A</t>
-        </is>
+        <v>1.5384865360200179</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
